--- a/docs/po/28102026-LCMS_Master_Data_Standardization_FastTrack_v1.0/LCMS_Master_Data_Standardization_Matrix_v1.0_20261028.xlsx
+++ b/docs/po/28102026-LCMS_Master_Data_Standardization_FastTrack_v1.0/LCMS_Master_Data_Standardization_Matrix_v1.0_20261028.xlsx
@@ -7,9 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MasterCatalogs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DbInventory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TESTLSS002" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matrix'!$A$1:$I$18</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -27,14 +31,20 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,11 +59,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,681 +433,2779 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Danh muc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>1. Nguon chuan va tenant</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2. API va man hinh</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>3. Hardcode, fallback, seed, import</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>4. Ma trung, di san, khong nhat quan (lcms_dev.db 2026-10-28)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>5. Validation, normalization, mapping</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>6. Anh huong nghiep vu, rating, lich su</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>GAP va cach da sua</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Test (ten ham)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Transport Mode</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>master_catalog_items.kind=transport_mode, tenant. Cot chuoi: orders/bills/shipments/transport_legs/transport_movements/rate_cards/pricing_rules.transport_mode, routes.transport_mode_code, surcharge_conditions.value_text khi dimension=transport_mode, ratings.context_json.transportMode. Khong FK.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>GET/POST /api/catalog. UpsertMasterCatalogItemCommand.cs. UpsertOrderCommand, UpdateBillContextCommand, EditOperationalReferenceCommand, UpsertShipmentCommand, UpsertTransportLegCommand, UpsertTransportMovementCommand, RateCardCommands, SaveRateCardDeclarationCommand, ComposeTariffCommand, PricingRuleCommands, SurchargeCommands, ImportOperationalBatchCommand, CreateRatingCommand. UI: admin/catalog/page.tsx, operations/legs/new/page.tsx, rate-cards/page.tsx, rate/page.tsx, compare/page.tsx, surcharges/page.tsx, surcharges/new/page.tsx, surcharges/[id]/page.tsx, RateCalculatorForm.tsx, CompareRatesForm.tsx, SurchargeForm.tsx, OperationalReferenceEditor.tsx, RateCardDeclarationForm.tsx.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Da go TRANSPORT_MODES trong apps/web/lib/create-workspace.ts va option value=air. Seed moi: DemoDataSeeder.EnsureDefaultCatalogAsync AIR/SEA/ROAD/RAIL. Seed cu: DemoVolumeCatalogSeeder chu thuong. Import: ImportOperationalBatchCommand, ImportRateCardsCommand.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Catalog chi air x1 active. orders 30 air/sea/road/rail. bills 32 air, 30 sea, 30 road, 30 rail, 10 null. shipments 30 moi ma. legs 120 null. movements 120 null. rate_cards 121 null, 2 air, 1 sea, ca 3 card published (NSE-AIR-VN-MY, TDNT_SGN_HAN, NSE-SEA-VN-MY). pricing_rules 3 air deu published. surcharge transport_mode 0. ratings context air x16. routes SGN-HAN mode air.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>TransportModeCatalog.ResolveAsync. Catalog co dong: phai SameMode active. Catalog trong: khong insert; chan do dai; chan MULTIMODAL ngoai Shipment; NewModeBlock chan WATER/EXPRESS tren rule moi. Ghi moi UPPERCASE. Doc: SameMode. OCEAN chi ho bien khi tinh W/M.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Match rating/surcharge khong gay vi hoa thuong. Stale khong bat khi chi doi cach viet. Snapshot cu giu air. AIR sang SEA van stale. Published card khong bi viet lai chu. Chua UPDATE 122 bill / 120 order / 120 shipment.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Bo ToLowerInvariant khi ghi. Dropdown lay catalog. So sanh semantic trong RatingStalenessService va UpdateBillContextCommand. Chua bulk DB, chua unique index CI.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>MasterDataStandardizationTests.HistoricalAir_SavedAsAir_DoesNotStale_SeaAndWeightStillDo_SnapshotStays; PublishedRateCard_KeepsStoredModeBytes_WhenTheSameModeIsSentInAnotherCase; ShipmentModePolicyTests; RateRatingBaselineTests.Uat02. PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Service Type</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>master_catalog_items.kind=service_type, tenant. Cot service_type_code tren bill/order/shipment/leg/route/pricing_rules.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Catalog API. EditOperationalReferenceCommand, UpdateBillContextCommand, RouteCommands. UI create-form-options.ts, OperationalReferenceEditor.tsx, selectableServices trong rate-field-policy.ts.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Seed DemoDataSeeder FREIGHT va AIR. DemoVolumeCatalogSeeder gan service AIR khi mode air. Khong importer service rieng.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Catalog FREIGHT 1, AIR 1 (di san). bills: null 130, FREIGHT 1, AIR 1. Rating context: FREIGHT 14, freight 1, master 1.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Co catalog thi ma phai khop ignore case, ghi UPPERCASE. AIR bi chan cho bill moi. Catalog trong khong insert dong.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Rating Matches ignore case. freight va FREIGHT khong stale. Khong sua context freight/master.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>UI bo AIR khoi lua chon moi. Chua sua seeder volume (quyet dinh PO).</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>RateRatingBaselineTests.Uat01_service_air_is_not_a_mode_and_stays_readable; rate-field-policy.test.ts hides AIR. PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Cost type</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>kind=cost_type, tenant.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Catalog API. rate-cards/new va [id]/edit listCatalog(cost_type). RateFieldPolicy.PublishBlock.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Seed FREIGHT, AP-FREIGHT, FUEL.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3 ma, moi ma 1, active. Cost TESTLSS002 dung FREIGHT va DONGGOI_SGN_HAN_MUA.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Upsert catalog UPPERCASE. Publish thieu loai chi phi thi chan.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Khong doi so tien cost.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Khong sua code cost trong luot nay.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Sprint4CostTests trong 579 PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Revenue type</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>kind=revenue_type, tenant.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Catalog API. rate card UI listCatalog(revenue_type). PublishBlock can RevenueTypeCode khi ban.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Seed FREIGHT-REV, AR-FREIGHT.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2 ma, moi ma 1, active.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Upsert UPPERCASE.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Khong doi cong thuc doanh thu.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Khong GAP moi.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>RatingModeTests.SellWeightBreak_SeedsExpectedRevenue_WithoutAnExtraComponent PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Pricing component</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>kind=pricing_component, tenant.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Catalog API. RateCardDeclarationForm chon khoan gia, khong o ma nhom tu do.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Seed FREIGHT. Khong fallback sinh FREIGHT.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1 ma FREIGHT active.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>ChargeCode ToUpperInvariant. PublishChargeMissing neu thieu.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Group rating theo charge hoa. Khong doi amount published.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Hardcode FREIGHT tren matrix da dong truoc do.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>rate-field-policy.test.ts; RateCardDeclarationForm.test.tsx UAT-13/16 PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Document type</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>kind=document_type, tenant. Ma luu chu thuong invoice, debit_note.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Catalog API. ReceiveFinancialDocumentCommand giu lowercase cho documentType.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Seed invoice, debit_note.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2 ma active, dung chu thuong.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Khong ep UPPERCASE trong luot nay.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Khong anh huong rating.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Khong sua.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Suite chung tu trong 579 PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Payment term</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>kind=payment_term, tenant.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Catalog API. Khong nam trong rating engine.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Seed NET15, NET30.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2 ma active, khong lech.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Upsert catalog UPPERCASE.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Khong doi AP/AR.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Khong GAP.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Khong test rieng; suite tai chinh PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Bang routes (tenant) va kind=transport_route.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>RouteCommands.UpsertRouteCommand. UI listRoutes trong create-form-options.ts. RatingEngine.RouteMatches.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Seed 120 ma VOL-RTE-0001..0120 trong catalog. Bang routes chi SGN-HAN.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>SGN-HAN mode air, service FREIGHT. 120 ma catalog moi ma 1, khong trung.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>ToStoredMode chi khi mode moi khac SameMode. Service tren tuyen phai active. Stale route trim ignore case.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Doi tuyen that van stale neu rule dung route. Published rate khong bi sua route.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Da bo ToLowerInvariant tren RouteCommands. Chua bulk air thanh AIR.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>RateRatingBaselineTests.Uat04; OperationalReferenceEditRatingContextTests.ContextChange_MarksOnlyUsedRatingsStale PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Bang locations va kind=location, ca hai tenant, khong FK.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Reference master location commands. UI listLocations. UpdateBillContextCommand.BindPlacesAsync.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Seed 120 VOL-LOC-* trong catalog. Bang locations: SGN, HAN.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Khong trung code trong locations. Catalog location khong trung SGN/HAN.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Khong ep UPPERCASE hang loat. Bind origin/destination sang location_id.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Stale origin/destination ignore case. Khong sua snapshot.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Hai nguon chua gop. De xuat PO.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>InputOptimizationInheritanceTests PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Bang currencies, global, khong tenant_id.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>listCurrencies. RateCardCatalog.EnsureCurrencyAsync trong RateCardCommands va SaveRateCardDeclarationCommand. UI create-form-options.ts.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>CurrencyCatalogSeeder.EnsureBaselineAsync.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15 ma ISO active, moi ma 1: AUD CAD CHF CNY EUR GBP HKD JPY KRW MYR SGD THB TWD USD VND. Khong co vnd thuong.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>CurrencyCode ToUpperInvariant va phai co trong currencies.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>RoundCurrency khong doi. Khong doi FX da luu.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Khong GAP hoa/thuong.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Suite tien te trong 579 PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Khong co bang tax_rates. So vat_rate tren rate_versions va surcharge_versions, theo version cua tenant.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>SaveRateCardDeclarationCommand, SurchargeCommands. UI form bang gia va SurchargeForm.tsx.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Khong seed 0/8/10. Khong hardcode vao mode.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Khong co bang ma thue de dem tung muc.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Giu so tren version published.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Cong thuc VAT khong doi.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Chua co master VAT. De xuat PO.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>ChargeProfitVatAcceptanceTests.Packaging_loss_uses_net_and_published_vat_stays_put; Component_charge_type_wins_and_legacy_surcharge_is_excluded_once PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Economic charge</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>economic_charge_types, tenant.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>EconomicChargeCommands. UI surcharges/page.tsx va SurchargeForm.tsx.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>EconomicChargeCatalogSeeder: DELIVERY FREIGHT FUEL HANDLING PICKUP REMOTE. Phu phi khong khai tren pricing rule.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6 ma, moi ma 1, active. surcharge_conditions: destination SBH 2, SWK 2. transport_mode 0. surcharge_versions published 6.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>ChargeCode UPPERCASE. Condition mode moi UPPERCASE. ConditionMatches OrdinalIgnoreCase. Hieu luc theo ngay lich IsBeforeEffectiveDay/IsAfterEffectiveDay.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Khong sua amount published. Phu phi cung ngay van ap dung.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Da sua ngay hieu luc va mode condition.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>IndependentSurchargeTests: IndependentFsc_CombinesWithBase_AndSkipsNonDg, Dedup_PicksTheMoreSpecificRule, BuyAndSell_WriteExpectedCostAndRevenue, OptionalRateCardScope_AppliesOnlyToThatCard, PercentageContainerAndFx_StoreTheLineSnapshot PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>commodity_types, tenant.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>listCommodities. PricingRuleCommands CommodityCode hoa. RatingEngine.Matches.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Seed demo. EXPRESS o day la loai hang, khong phai transport EXPRESS.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5 ma active, DG=0: COSMETICS, COSMETICS_FOOD, DRY_FOOD, EXPRESS, GENERAL. Khong trung.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Khong bulk rename.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Doi commodity_type_id co the stale neu rule co commodity.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Khong GAP hoa/thuong.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>BuyRatingLegTests.LegSuggestion_UsesLegCommodity_NotTheBill PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Party role</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>party_roles.role_code, tenant. Quy uoc chu thuong.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>PartyRoleCommands, BusinessPartyCommands. UI PartyTypeahead.tsx.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Khong seed UPPERCASE. PartyCatalog so sau ToLowerInvariant.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>484 dong: customer/payee/payer/vendor moi role 121, active.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Giu chu thuong. Khong ToUpper.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Doi customer_party_id hoac vendor_party_id lam stale. Khong sua dong cu.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Khong GAP.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Suite doi tac trong 579 PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Incoterm</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Khong co kind, khong co bang. Cot bills.incoterm_code va orders.incoterm_code.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Khong API catalog. UI hang INCOTERMS trong apps/web/lib/create-workspace.ts: EXW FCA FOB CIF CFR DAP DDP.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Hardcode ICC. Khong seed. Khong import.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>bills.incoterm_code NULL 132/132.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Khong normalize server trong luot nay.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Khong nam trong RatingEngine.Matches. Khong stale.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Chua catalog hoa. De xuat PO.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Khong ham rieng. Hang UI khong doi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Special flags</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Khong bang master. Chuoi dg, reefer, oog, other tren context hang.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EditOperationalReferenceCommand nhanh Flags. UI SPECIAL_FLAGS trong create-workspace.ts. SurchargeRating dimension dangerous_goods.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Hardcode 4 co. Khong seed bang.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5 commodity deu is_dangerous_goods=0. Khong cot ma de COUNT.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Giu chu thuong. Tach khoi transport mode.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Phu phi DG khong ap hang khong DG. Khong sua co cu.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Khong GAP voi mode.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>IndependentSurchargeTests.IndependentFsc_CombinesWithBase_AndSkipsNonDg PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>UOM</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>operational_measurements, tenant. UOM kg, cbm, wm/W/M, pcs.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>EditOperationalReferenceCommand, ChargeableWeightPolicy. UI opref-edit.ts.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Khong catalog UOM. UomFor chon W/M khi IsSeaFamily.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>120 leg mode null nen khong suy CW tu mode rieng.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>IsSea/IsAir dung ShipmentModePolicy.Normalize, khong ToLowerInvariant. WATER khong dung W/M.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Doi gross/volume/CW van stale dung basis. Khong ghi de measurement khi chi doi cach viet mode.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Da sua CW nhan mode hoa.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>ShipmentModePolicyTests.Water_DoesNotUseSeaChargeableWeight; MasterDataStandardizationTests (gross 85 sang 120) PASS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I18"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Danh muc</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Nguon</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Tenant</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Quy tac ma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>GAP da sua</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Ket qua</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Bang</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Cot hoac nhom</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Gia tri</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>So dong</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Ghi chu</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Transport Mode</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>master_catalog_items.kind=transport_mode</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>UPPERCASE; WATER/EXPRESS khong gop; MULTIMODAL chi Shipment</t>
-        </is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bo ToLower khi ghi; dropdown catalog; SameMode</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>MasterDataStandardizationTests; ShipmentModePolicyTests</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>chu thuong</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Service Type</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>master_catalog_items.kind=service_type</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>UPPERCASE FREIGHT; AIR la ma di san</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Ghi hoa; khong tu sinh khi catalog trong</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>RateRatingBaselineTests.Uat01</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cost type</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>master_catalog_items.kind=cost_type</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>UPPERCASE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Khong doi so tien</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Suite cost</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Revenue type</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>master_catalog_items.kind=revenue_type</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>UPPERCASE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Khong doi so tien</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Suite revenue</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pricing component</t>
+          <t>bills</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kind=pricing_component</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>UPPERCASE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Khong hardcode FREIGHT tren ma tran</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>rate-field-policy.test.ts</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Document type</t>
+          <t>bills</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kind=document_type</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Giu invoice/debit_note</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Khong ep UPPERCASE</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Khong doi hanh vi</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Payment term</t>
+          <t>bills</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kind=payment_term</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NET30</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Khong sua</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Khong doi hanh vi</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>bills</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>routes + kind=transport_route</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SGN-HAN giu nguyen</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Stale so route trim ignore case</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>OperationalReferenceEditRatingContextTests</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>bills</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>locations</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>IATA/UNLOCODE</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Khong ep UPPERCASE hang loat</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Khong migration</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>(NULL)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>shipments</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>currencies</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ISO VND/USD</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Khong doi</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Suite tien te</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VAT</t>
+          <t>shipments</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rate_versions.vat_rate</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>theo bang gia</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>So 0/8/10</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Khong doi cong thuc</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ChargeProfitVatAcceptanceTests</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Economic charge</t>
+          <t>shipments</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>economic_charge_types</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>FREIGHT/PICKUP UPPERCASE</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Phu phi cung ngay van ap dung</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>IndependentSurchargeTests</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Commodity</t>
+          <t>shipments</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>commodity_types</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>GENERAL UPPERCASE khi ghi rule</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Khong bulk update</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Rating commodity</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>rail</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Party role</t>
+          <t>transport_legs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>party_roles</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>customer/vendor chu thuong</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Khong ep UPPERCASE</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Khong doi</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>(NULL)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>120</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Incoterm</t>
+          <t>transport_movements</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bill context</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>chung tu</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>FOB/CIF</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Dropdown ICC, chua co kind catalog</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>De xuat PO</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
+          <t>(NULL)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>120</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Special flags</t>
+          <t>rate_cards</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cargo context</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>dg/reefer/oog chu thuong</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Giu chu thuong</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>IndependentFsc_CombinesWithBase_AndSkipsNonDg</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>(NULL)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>121</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UOM</t>
+          <t>rate_cards</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>operational_measurements</t>
+          <t>transport_mode</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>tenant</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>kg/cbm/wm</t>
-        </is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CW doc mode khong phan biet hoa thuong</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ShipmentModePolicyTests</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>published NSE-AIR-VN-MY, TDNT_SGN_HAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>rate_cards</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>transport_mode</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>published NSE-SEA-VN-MY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>pricing_rules</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>transport_mode</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>(NULL)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>126</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>pricing_rules</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>transport_mode</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>tat ca published</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>routes</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>transport_mode_code</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SGN-HAN service FREIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>surcharge_conditions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>destination</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SBH</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>surcharge_conditions</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>destination</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>surcharge_conditions</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>transport_mode</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ratings</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>context.transportMode</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>16</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ratings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>context.serviceType</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FREIGHT</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ratings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>context.serviceType</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>freight</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>khong phai TESTLSS002</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ratings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>context.serviceType</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>VOL-BILL-0120</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ratings</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>stale_at</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>16</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>rate_versions</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>125</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>rate_versions</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>surcharge_versions</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>publish_status</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>master_catalog_items</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>cost_type</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AP-FREIGHT, FREIGHT, FUEL</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>moi ma 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>master_catalog_items</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>document_type</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>debit_note, invoice</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>master_catalog_items</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VOL-LOC-0001..0120</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>120</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>moi ma 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>master_catalog_items</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>payment_term</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NET15, NET30</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>master_catalog_items</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>pricing_component</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>FREIGHT</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>master_catalog_items</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>revenue_type</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AR-FREIGHT, FREIGHT-REV</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>master_catalog_items</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>service_type</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AIR, FREIGHT</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AIR la di san</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>master_catalog_items</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>transport_mode</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>chu thuong</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>master_catalog_items</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>transport_route</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VOL-RTE-0001..0120</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>120</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>moi ma 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>currencies</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>15 ISO</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>15</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AUD CAD CHF CNY EUR GBP HKD JPY KRW MYR SGD THB TWD USD VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>commodity_types</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5 ma</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>COSMETICS COSMETICS_FOOD DRY_FOOD EXPRESS GENERAL; DG=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>economic_charge_types</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6 ma</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DELIVERY FREIGHT FUEL HANDLING PICKUP REMOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SGN, HAN</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>airport VN</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>party_roles</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>role_code</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>customer, payee, payer, vendor</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>484</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>121 moi role</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>bills</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>service_type_code</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NULL / FREIGHT / AIR</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>132</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>130 / 1 / 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>bills</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>incoterm_code</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>132</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>audit_events</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>rate_card.*</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>51</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>version_created 24, declaration_changed 24, published 3; khong co rating.mark_stale</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>rating_id</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>rated_at_utc</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>party_type</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>context_type</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>transportMode</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>rate_version_id</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>stale_at</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>stale_reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>01A16DC5-FF89-7B71-8C52-E95C69083DD1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:57:34.9866322+00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>01A16DBD-BFFA-7065-A883-7260C83D4CBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01A16DC6-035B-7DA4-AC25-DBF18CEFC885</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:57:35.9630898+00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>01A16DBD-BFFA-7065-A883-7260C83D4CBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>01A16DC6-03B6-70FE-8F91-505DC713566B</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:57:36.0548013+00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>01A16DBD-BFFA-7065-A883-7260C83D4CBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>01A16DC6-0414-7987-BA70-016795D4B351</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:57:36.1488027+00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>01A16DBD-BFFA-7065-A883-7260C83D4CBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01A16DC6-0490-7A3D-82B0-2E0EA580B23F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:57:36.2721294+00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>01A16CF7-3B7A-7F90-8A6E-DEDDBF487F62</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>01A16DC6-04D8-7E03-9D63-EA7CB29884C9</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:57:36.3442952+00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>01A16DBD-BFFA-7065-A883-7260C83D4CBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>01A16DD2-5DDE-7575-8836-7B4F16B69A65</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:11:05.5663847+00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>01A16DD0-D08F-72D4-9C3C-01C3E108EFF6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>01A16DD2-5EAC-767A-8B9F-6918F85DAB4F</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:11:05.7728923+00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>01A16DD0-D08F-72D4-9C3C-01C3E108EFF6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>01A16DD2-5F45-7524-B774-EE45A41F7EE4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:11:05.9255797+00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>01A16DD0-D08F-72D4-9C3C-01C3E108EFF6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01A16DD2-614E-70DA-ADF3-43110EC494A2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:11:06.4468+00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>01A16DD0-D08F-72D4-9C3C-01C3E108EFF6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>01A16DD2-6266-712F-ACFA-75DA3918DBCE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:11:06.7261409+00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>01A16CF7-3B7A-7F90-8A6E-DEDDBF487F62</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>01A16DD2-62D3-7B71-9C81-67B3E1C9B8B6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:11:06.8352429+00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>01A16DD0-D08F-72D4-9C3C-01C3E108EFF6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>01A16DD7-3054-7549-A197-CE93787701AC</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:16:21.5888635+00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>01A16DD6-8B84-78AA-A9C8-509E0224A2CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>01A16DD7-F111-78AA-A9C8-509E0224A2CF</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-10-27T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>bill</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1740000</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>actual_or_formula</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>01A16DD6-8B84-78AA-A9C8-509E0224A2CF</t>
         </is>
       </c>
     </row>
